--- a/Data_Table/증강 특수 효과 테이블.xlsx
+++ b/Data_Table/증강 특수 효과 테이블.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -612,65 +612,65 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Snowball</t>
+          <t>Blades</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>눈덩이 굴리기</t>
+          <t>회전 치즈 칼날</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Blades</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>회전 치즈 칼날</t>
+          <t>천둥 번개</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>170</v>
-      </c>
       <c r="F6" s="1" t="n">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>3</v>
@@ -678,29 +678,29 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>83004</v>
+        <v>83005</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>ClickBomb</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>천둥 번개</t>
+          <t>클릭 폭격</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>6</v>
+        <v>0.12</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
@@ -711,59 +711,59 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>83005</v>
+        <v>83009</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>ClickBomb</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>클릭 폭격</t>
+          <t>쥐 토네이도</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>83006</v>
+        <v>83010</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Mitosis</t>
+          <t>WallQuake</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>세포 분열</t>
+          <t>연쇄 붕괴</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
         <v>0.15</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>0</v>
@@ -777,23 +777,23 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Rewind</t>
+          <t>PromoteBoom</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>시간 역행</t>
+          <t>승급 폭죽</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>0</v>
@@ -805,28 +805,28 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>83008</v>
+        <v>83012</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>UltEcho</t>
+          <t>Jackpot</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>필살기 메아리</t>
+          <t>잭팟</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>0</v>
@@ -843,59 +843,59 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>83009</v>
+        <v>83013</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Midas</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>쥐 토네이도</t>
+          <t>미다스의 앞니</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>83010</v>
+        <v>83014</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>WallQuake</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>연쇄 붕괴</t>
+          <t>쥐 탑 쌓기</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.15</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>0</v>
@@ -904,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>PromoteBoom</t>
+          <t>CheeseRain</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>승급 폭죽</t>
+          <t>치즈 비</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>0</v>
@@ -937,40 +937,271 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>83012</v>
+        <v>83016</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Jackpot</t>
+          <t>Unify</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>잭팟</t>
+          <t>골든 햄스터 생쥐</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.2</v>
+        <v>10006</v>
       </c>
       <c r="E15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>83017</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Unify</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>판다 잠옷 정글리안 생쥐</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>10015</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>83018</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Clones</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>분신 소환</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="n">
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>83019</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Meteor</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>운석 소환</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>83020</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>장난감 기차</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>83021</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Unify</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>스케이터 생쥐</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>10032</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>83022</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Unify</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>맘스땃쥐 생쥐</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>10085</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>83023</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Unify</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>5G 생쥐</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>10087</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1147,54 +1378,54 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Snowball</t>
+          <t>Blades</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>부술 때마다 공격력 +</t>
+          <t>확률 (물건을 칠 때마다)</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>최대</t>
+          <t>칼날 수</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>반경</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>피해 (평균 공격력 ×)</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>지속 (초)</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>이번 층에서 물건을 부술 때마다 쥐 공격력 +p1 (최대 p2, 층이 바뀌면 처음부터)</t>
+          <t>쥐가 물건을 칠 때 p1 확률로 (묘기와 따로) 그 쥐 둘레를 치즈 칼날 p2 개가 p5 초 돌며 공격 (반경 p3, 평균 공격력 × p4)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Blades</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>칼날 수</t>
+          <t>간격 (초)</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>반경</t>
+          <t>번개 수</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -1204,34 +1435,34 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>같은 대상 다시 때리는 간격 (초)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>회전 속도 (바퀴/초)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>쥐 무리 가운데를 도는 치즈 칼날 p1 개: 닿은 물건·고양이·사람·보스에 평균 공격력 × p3</t>
+          <t>p1 초마다 방 위 먹구름에서 화면 속 대상 p2 곳에 번개 (예고 없음, 평균 공격력 × p3)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>ClickBomb</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>간격 (초)</t>
+          <t>확률 (클릭마다)</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>대상 수</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -1241,7 +1472,7 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>폭발 반경</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -1251,66 +1482,66 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>p1 초마다 화면 속 대상 p2 곳에 번개 (평균 공격력 × p3)</t>
+          <t>클릭 총공격 중 누를 때마다 p1 확률로 누른 곳에 작은 폭발 (반경 p4, 평균 공격력 × p3)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ClickBomb</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>폭발 수</t>
+          <t>간격 (초)</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>퍼짐 반경</t>
+          <t>지속 (초)</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>피해 (평균 공격력 ×)</t>
+          <t>반경</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>폭발 반경</t>
+          <t>초당 피해 (평균 공격력 ×)</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이동 속도</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>클릭 총공격 때 누른 곳 둘레 p2 안에 작은 폭발 p1 번 (반경 p4, 평균 공격력 × p3)</t>
+          <t>p1 초마다 쥐 토네이도가 (붉은 원 예고 뒤) p2 초 동안 열린 방을 휩씀: 반경 p3 안 물건을 끌어당기며 초당 평균 공격력 × p4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Mitosis</t>
+          <t>WallQuake</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>확률</t>
+          <t>다른 벽 체력 감소 (최대 체력 비율)</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>임시 쥐 시간 (초)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>동시에 최대</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -1325,24 +1556,24 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>물건을 부수면 p1 확률로 그 자리에 임시 쥐 (p2 초, 최대 p3 마리)</t>
+          <t>벽 하나가 무너지면 남은 벽들이 최대 체력의 p1 만큼 깎임</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Rewind</t>
+          <t>PromoteBoom</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>되돌리는 시간 (초)</t>
+          <t>반경</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>판당 횟수</t>
+          <t>피해 (평균 공격력 ×)</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -1362,14 +1593,14 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>제한시간이 0 이 되면 한 번 p1 초를 되돌림 (판당 p2 번)</t>
+          <t>승급할 때 새 쥐 자리에서 폭죽 3발이 솟았다 폭발 (반경 p1, 평균 공격력 × p2)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>UltEcho</t>
+          <t>Jackpot</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -1379,7 +1610,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>연구자료 배율</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -1399,66 +1630,66 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>필살기가 끝나면 p1 확률로 다른 쥐의 필살기가 바로 한 번 더</t>
+          <t>층 클리어 때 p1 확률로 연구자료 × p2 (잭팟!, 화면 구석 슬롯머신)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Midas</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>간격 (초)</t>
+          <t>황금 물건 치즈 +</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>지속 (초)</t>
+          <t>반짝임 배율</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>반경</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>초당 피해 (평균 공격력 ×)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>이동 속도</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>p1 초마다 쥐 토네이도가 p2 초 동안 열린 방을 휩씀: 반경 p3 안 물건을 끌어당기며 초당 평균 공격력 × p4</t>
+          <t>황금 물건을 부수면 치즈 +p1 · 황금 물건이 p2 배 자주 반짝임</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WallQuake</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>다른 벽 체력 감소 (최대 체력 비율)</t>
+          <t>탑 수</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탑마다 마리 수</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>나오는 조건 (쥐 마리 수 이상)</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -1473,29 +1704,29 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>벽 하나가 무너지면 남은 벽들이 최대 체력의 p1 만큼 깎임</t>
+          <t>장착하는 순간 쥐 p2 마리를 합쳐 1마리 탑 (능력치 합산, 특성 = 1층 쥐) p1 개, 판 끝까지. 쥐가 p3 마리 이상일 때만 고르기에 나옴</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>PromoteBoom</t>
+          <t>CheeseRain</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>반경</t>
+          <t>간격 (초)</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>피해 (평균 공격력 ×)</t>
+          <t>지속 (초)</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>치즈 +</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -1510,44 +1741,155 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>승급할 때 새 쥐 자리에서 폭죽 폭발 (반경 p1, 평균 공격력 × p2)</t>
+          <t>p1 초마다 방 천장 치즈 구름에서 p2 초 동안 치즈 비: 그동안 치즈 +p3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Jackpot</t>
+          <t>Unify</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>확률</t>
+          <t>바꿀 쥐 character_id</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>연구자료 배율</t>
+          <t>쥐 등급 (1 일반 · 2 레어 · 3 에픽)</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이동 속도 배율</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>박치기 피해 +</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>패티 최대</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 때 p1 확률로 연구자료 × p2 (잭팟!)</t>
+          <t>그 등급 쥐 전원 (이후 태어나는 쥐도) → p1 쥐. 같은 등급 Unify 끼리 동시 장착 불가. 빼면 이미 바뀐 쥐는 종류 그대로 · 동작만 원래</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Clones</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>간격 (초)</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>마리 수</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>지속 (초)</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>크기 배율</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>예고 (초)</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>p1 초마다 가장 강한 쥐의 분신 p2 마리가 방 네 구석에 (붉은 원 p5 초 예고) 거대한 모습 (×p4) 으로 p3 초 동안 싸움 (인구 안 차지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Meteor</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>간격 (초)</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>피해 (평균 공격력 ×)</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>예고 (초)</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>그림 크기</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>p1 초마다 붉은 원 p4 초 예고 뒤 큰 치즈 운석 (그림 p5) 낙하: 반경 p2, 평균 공격력 × p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>간격 (초)</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>피해 (평균 공격력 ×)</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>폭 (위아래)</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>p1 초마다 장난감 기차가 맵 한쪽 끝에서 반대편 끝까지: 지나간 길 (폭 p4) 의 물건 튕김 + 평균 공격력 × p3</t>
         </is>
       </c>
     </row>

--- a/Data_Table/증강 특수 효과 테이블.xlsx
+++ b/Data_Table/증강 특수 효과 테이블.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Special" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Special_Type" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Special" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Special_Type" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -667,10 +667,10 @@
         <v>15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>3</v>
@@ -931,10 +931,10 @@
         <v>0.3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>3</v>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>구름 머무는 시간 (초)</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>번개 범위 (구름 아래 반경)</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>p1 초마다 방 위 먹구름에서 화면 속 대상 p2 곳에 번개 (예고 없음, 평균 공격력 × p3)</t>
+          <t>p1 초마다 대상 근처 맵에 먹구름 소환 → p4 초 동안 바닥 원 (반경 p5) 안 대상에 번개 p2 번 (평균 공격력 × p3). 2026-10-23 화면 위 상시 구름 없앰</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>층 클리어 때 p1 확률로 연구자료 × p2 (잭팟!, 화면 구석 슬롯머신)</t>
+          <t>층 클리어 때 p1 확률로 연구자료 × p2 (잭팟!, 계단 자리에 슬롯머신)</t>
         </is>
       </c>
     </row>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>초당 피해 (평균 공격력 ×)</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>비 범위 (구름 아래 반경)</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>p1 초마다 방 천장 치즈 구름에서 p2 초 동안 치즈 비: 그동안 치즈 +p3</t>
+          <t>p1 초마다 맵에 치즈 구름 소환 → p2 초 동안 바닥 원 (반경 p5) 안에 치즈 비: 초당 평균 공격력 × p4 · 그동안 치즈 +p3</t>
         </is>
       </c>
     </row>
